--- a/synthese eden.xlsx
+++ b/synthese eden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eden/portefolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B28DCA-C931-754B-A2F1-4A5139BD599E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D04EAB-1207-AF46-8165-4A1DB359E62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -752,11 +752,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -780,17 +791,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1111,56 +1111,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="43" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="44"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="32" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1172,22 +1172,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="40" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1210,8 +1210,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="40"/>
-      <c r="B7" s="36"/>
+      <c r="A7" s="45"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
@@ -1267,16 +1267,16 @@
       <c r="AQ7" s="1"/>
     </row>
     <row r="8" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="43"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1710,16 +1710,16 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="31"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" spans="1:8" s="1" customFormat="1" ht="110" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="16" t="s">
@@ -1806,16 +1806,16 @@
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
@@ -1828,11 +1828,11 @@
       <c r="D28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
       <c r="H28" s="15"/>
     </row>
     <row r="29" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
@@ -1907,11 +1907,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -1919,6 +1914,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/synthese eden.xlsx
+++ b/synthese eden.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eden/portefolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D04EAB-1207-AF46-8165-4A1DB359E62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABA22D8-2285-6345-8B9E-88B3F81E93BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -728,9 +728,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -752,22 +749,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -790,6 +776,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1111,56 +1111,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="29" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="37" t="s">
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1172,22 +1172,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="34" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1210,8 +1210,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="45"/>
-      <c r="B7" s="41"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
@@ -1267,16 +1267,16 @@
       <c r="AQ7" s="1"/>
     </row>
     <row r="8" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="43"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1324,11 +1324,13 @@
         <v>24</v>
       </c>
       <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14" t="s">
+      <c r="E9" s="14" t="s">
         <v>24</v>
       </c>
+      <c r="F9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="14"/>
       <c r="H9" s="15"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1379,8 +1381,12 @@
       <c r="D10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="E10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="G10" s="13"/>
       <c r="H10" s="15"/>
       <c r="I10" s="1"/>
@@ -1514,7 +1520,7 @@
       <c r="B13" s="11"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="E13" s="47"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="15"/>
@@ -1710,16 +1716,16 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" spans="1:8" s="1" customFormat="1" ht="110" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="16" t="s">
@@ -1737,9 +1743,7 @@
       <c r="E20" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="F20" s="18"/>
       <c r="G20" s="18" t="s">
         <v>24</v>
       </c>
@@ -1806,16 +1810,16 @@
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="30"/>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
@@ -1824,15 +1828,17 @@
       <c r="B28" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="13"/>
+      <c r="C28" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="D28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="21"/>
+      <c r="E28" s="20" t="s">
+        <v>24</v>
+      </c>
       <c r="F28" s="13"/>
-      <c r="G28" s="20" t="s">
-        <v>24</v>
-      </c>
+      <c r="G28" s="20"/>
       <c r="H28" s="15"/>
     </row>
     <row r="29" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
@@ -1886,27 +1892,32 @@
       <c r="H33" s="15"/>
     </row>
     <row r="34" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="22"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="25"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" spans="1:8" s="1" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="26"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -1914,11 +1925,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/synthese eden.xlsx
+++ b/synthese eden.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eden/portefolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABA22D8-2285-6345-8B9E-88B3F81E93BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA1444C-1055-F54C-A8CB-55E290496ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -169,6 +169,12 @@
   </si>
   <si>
     <t>SESSION 2026</t>
+  </si>
+  <si>
+    <t>Portfolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/12/2025 - 20/03/2026 </t>
   </si>
 </sst>
 </file>
@@ -668,7 +674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -749,11 +755,28 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -776,20 +799,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1111,56 +1120,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="43"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:43" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
     </row>
     <row r="3" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="33"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1172,22 +1181,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="41" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1210,8 +1219,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" ht="325" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="39"/>
-      <c r="B7" s="35"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="42"/>
       <c r="C7" s="8" t="s">
         <v>28</v>
       </c>
@@ -1267,16 +1276,16 @@
       <c r="AQ7" s="1"/>
     </row>
     <row r="8" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="37"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1323,7 +1332,9 @@
       <c r="C9" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="14" t="s">
+        <v>24</v>
+      </c>
       <c r="E9" s="14" t="s">
         <v>24</v>
       </c>
@@ -1426,14 +1437,20 @@
       <c r="AQ10" s="1"/>
     </row>
     <row r="11" spans="1:43" ht="40" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
+      <c r="A11" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="29"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1520,7 +1537,7 @@
       <c r="B13" s="11"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
-      <c r="E13" s="47"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="13"/>
       <c r="G13" s="13"/>
       <c r="H13" s="15"/>
@@ -1716,16 +1733,16 @@
       <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="30"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="34"/>
     </row>
     <row r="20" spans="1:8" s="1" customFormat="1" ht="110" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="16" t="s">
@@ -1810,16 +1827,16 @@
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:8" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="30"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="34"/>
     </row>
     <row r="28" spans="1:8" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10" t="s">
@@ -1913,11 +1930,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
@@ -1925,6 +1937,11 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
